--- a/macros/CDF_Toolkit_CATIA_no_password/对照表.xlsx
+++ b/macros/CDF_Toolkit_CATIA_no_password/对照表.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CATIA_Related\CATIA-Copilot\macros\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CATIA-Copilot-Project\CATIA-Copilot\macros\CDF_Toolkit_CATIA_no_password\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D5AF38-A807-405E-88F0-A4E84F5DCD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BA4B52-879E-493C-B179-170DBF46AA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8145" yWindow="4050" windowWidth="38700" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="176">
   <si>
     <t>调用的 exe</t>
   </si>
@@ -466,6 +467,112 @@
   <si>
     <t>打开当前工作文件夹</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>有价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注册表路径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>已运行次数</t>
+  </si>
+  <si>
+    <t>0，每次启动 +1</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>首次运行日期</t>
+  </si>
+  <si>
+    <t>机器码</t>
+  </si>
+  <si>
+    <t>首次运行时根据其他 8 个 S3 计算生成</t>
+  </si>
+  <si>
+    <t>S4</t>
+  </si>
+  <si>
+    <t>注册码</t>
+  </si>
+  <si>
+    <t>空（注册后写入）</t>
+  </si>
+  <si>
+    <t>工具标识</t>
+  </si>
+  <si>
+    <t>CATIA</t>
+  </si>
+  <si>
+    <t>CATIA_AutoDrw</t>
+  </si>
+  <si>
+    <t>CATIA_CNCList</t>
+  </si>
+  <si>
+    <t>FastHole</t>
+  </si>
+  <si>
+    <t>FastBolt</t>
+  </si>
+  <si>
+    <t>CATIA_New1</t>
+  </si>
+  <si>
+    <t>CATIA_New2</t>
+  </si>
+  <si>
+    <t>（第 8 个，默认）</t>
+  </si>
+  <si>
+    <t>"YYYYMMDD" 格式，写入一次不再修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REG_SZ</t>
+  </si>
+  <si>
+    <t>HKCU\Software\Microsoft</t>
+  </si>
+  <si>
+    <t>HKCU\Software\Microsoft\Windows</t>
+  </si>
+  <si>
+    <t>HKCU\Network</t>
+  </si>
+  <si>
+    <t>HKCU\Console</t>
+  </si>
+  <si>
+    <t>HKCU\Software\Microsoft\TabletPC</t>
+  </si>
+  <si>
+    <t>HKCU\Software\Microsoft\Calc</t>
+  </si>
+  <si>
+    <t>HKCU\Software\Microsoft\Accessibility</t>
+  </si>
+  <si>
+    <t>HKCU\Software\Microsoft\Office</t>
+  </si>
+  <si>
+    <t>HKCU\Software\Microsoft\TablePC</t>
   </si>
 </sst>
 </file>
@@ -496,7 +603,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -504,17 +611,145 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -790,763 +1025,1175 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="47.75" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="46.375" customWidth="1"/>
+    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="36.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="E2:E50 F4">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E51 F4">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E50" xr:uid="{43C2B800-E5A7-424F-97DE-9891E4A36057}">
+      <formula1>"Yes, No, N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B05E3D-0781-462D-989D-2D647FEAD535}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="C1" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>148</v>
+      </c>
+      <c r="B2" t="s">
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="D2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>156</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>157</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>128</v>
-      </c>
-      <c r="E12" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E15" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>128</v>
-      </c>
-      <c r="E18" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" t="s">
-        <v>128</v>
-      </c>
-      <c r="E19" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" t="s">
-        <v>139</v>
-      </c>
-      <c r="F22" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" t="s">
-        <v>139</v>
-      </c>
-      <c r="F23" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" t="s">
-        <v>82</v>
-      </c>
-      <c r="D24" t="s">
-        <v>130</v>
-      </c>
-      <c r="E24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" t="s">
-        <v>130</v>
-      </c>
-      <c r="E26" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" t="s">
-        <v>102</v>
-      </c>
-      <c r="E27" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" t="s">
-        <v>129</v>
-      </c>
-      <c r="E29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E30" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E31" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" t="s">
-        <v>102</v>
-      </c>
-      <c r="E32" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" t="s">
-        <v>107</v>
-      </c>
-      <c r="D33" t="s">
-        <v>102</v>
-      </c>
-      <c r="E33" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>130</v>
-      </c>
-      <c r="E34" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>112</v>
-      </c>
-      <c r="C35" t="s">
-        <v>103</v>
-      </c>
-      <c r="D35" t="s">
-        <v>128</v>
-      </c>
-      <c r="E35" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" t="s">
-        <v>132</v>
-      </c>
-      <c r="E36" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>114</v>
-      </c>
-      <c r="C37" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" t="s">
-        <v>130</v>
-      </c>
-      <c r="E37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C38" t="s">
-        <v>127</v>
-      </c>
-      <c r="D38" t="s">
-        <v>130</v>
-      </c>
-      <c r="E38" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>116</v>
-      </c>
-      <c r="C39" t="s">
-        <v>141</v>
-      </c>
-      <c r="E39" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C40" t="s">
-        <v>87</v>
-      </c>
-      <c r="E40" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>118</v>
-      </c>
-      <c r="C41" t="s">
-        <v>91</v>
-      </c>
-      <c r="D41" t="s">
-        <v>128</v>
-      </c>
-      <c r="E41" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>119</v>
-      </c>
-      <c r="C42" t="s">
-        <v>92</v>
-      </c>
-      <c r="D42" t="s">
-        <v>128</v>
-      </c>
-      <c r="E42" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>120</v>
-      </c>
-      <c r="C43" t="s">
-        <v>93</v>
-      </c>
-      <c r="D43" t="s">
-        <v>131</v>
-      </c>
-      <c r="E43" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>121</v>
-      </c>
-      <c r="C44" t="s">
-        <v>95</v>
-      </c>
-      <c r="D44" t="s">
-        <v>128</v>
-      </c>
-      <c r="E44" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D45" t="s">
-        <v>128</v>
-      </c>
-      <c r="E45" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>111</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
